--- a/demo_data/sectors/insaat_taahhut/mizan_cur.xlsx
+++ b/demo_data/sectors/insaat_taahhut/mizan_cur.xlsx
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>746807.34</v>
+        <v>746807.35</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>37429.03</v>
+        <v>37429.02</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3066575.34</v>
+        <v>3504657.54</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1752328.77</v>
+        <v>2628493.15</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -919,16 +919,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>170.01</t>
+          <t>150.03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Yıllara Yaygın İnşaat Maliyetleri (Proje A)</t>
+          <t>Şantiye Yapı Malzemeleri &amp; Yalıtım</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3942739.73</v>
+        <v>2628493.15</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -1431,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>9483767.12999999</v>
+        <v>9483767.130000001</v>
       </c>
     </row>
     <row r="57">
